--- a/data/guida_competenze.xlsx
+++ b/data/guida_competenze.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MB6982\Desktop\Competenze\Dataset Competenze\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16813CEA-1F8E-4AEE-87D6-6DB36E63FFFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2713CB9-830E-4C86-966C-6DBE87DAC7C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{13FF30BE-F8A4-4DB4-BD62-82FA1E207AFB}"/>
   </bookViews>
   <sheets>
-    <sheet name="Foglio1" sheetId="4" r:id="rId1"/>
+    <sheet name="File" sheetId="4" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Foglio1!$A$1:$D$190</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">File!$A$1:$D$196</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="760" uniqueCount="436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="462">
   <si>
     <t>Codice</t>
   </si>
@@ -602,18 +602,6 @@
     <t>Integrare farmacovigilanza e segnalazione eventi avversi nei percorsi di cura oncologici</t>
   </si>
   <si>
-    <t>Genomica e medicina personalizzata</t>
-  </si>
-  <si>
-    <t>Integrare risultati di test genetici e biomarcatori nella pianificazione terapeutica personalizzata</t>
-  </si>
-  <si>
-    <t>Valutare implicazioni cliniche etiche e legali delle tecnologie genomiche supportando decisioni informate</t>
-  </si>
-  <si>
-    <t>Collaborare alla gestione di percorsi di screening genetico e consulenza oncogenetica</t>
-  </si>
-  <si>
     <t>Navigazione oncologica e survivorship avanzata</t>
   </si>
   <si>
@@ -647,15 +635,6 @@
     <t>CHM6</t>
   </si>
   <si>
-    <t>GEN1</t>
-  </si>
-  <si>
-    <t>GEN2</t>
-  </si>
-  <si>
-    <t>GEN3</t>
-  </si>
-  <si>
     <t>NAV3</t>
   </si>
   <si>
@@ -854,9 +833,6 @@
     <t>Valutare e gestire rischio di ittero neonatale interpretando valori di bilirubina secondo età post-natale</t>
   </si>
   <si>
-    <t>Mantenere stabilità termica prevenendo ipotermia e ipertermia</t>
-  </si>
-  <si>
     <t>Riconoscere segni di infezione neonatale attivando tempestivamente valutazione medica</t>
   </si>
   <si>
@@ -1016,63 +992,18 @@
     <t>Valutazione clinica psichiatrica avanzata</t>
   </si>
   <si>
-    <t>Condurre valutazione dello stato mentale integrando osservazione clinica colloquio e strumenti standardizzati</t>
-  </si>
-  <si>
-    <t>Identificare sintomi psicotici affettivi cognitivi e comportamentali valutandone gravità e impatto funzionale</t>
-  </si>
-  <si>
-    <t>Valutare rischio suicidario e autolesivo attraverso assessment strutturato e rivalutazione dinamica</t>
-  </si>
-  <si>
     <t>Gestione crisi e rischio psichiatrico</t>
   </si>
   <si>
-    <t>Gestire crisi comportamentali acute adottando tecniche di de-escalation e contenimento sicuro</t>
-  </si>
-  <si>
-    <t>Attuare interventi in caso di agitazione psicomotoria garantendo sicurezza di assistito e operatori</t>
-  </si>
-  <si>
-    <t>Riconoscere segni precoci di scompenso psichico attivando interventi preventivi</t>
-  </si>
-  <si>
     <t>Terapie psicofarmacologiche e trattamenti specialistici</t>
   </si>
   <si>
-    <t>Monitorare efficacia e effetti collaterali di psicofarmaci inclusi antipsicotici stabilizzatori e antidepressivi</t>
-  </si>
-  <si>
-    <t>Gestire terapie long-acting e trattamenti complessi garantendo aderenza e sicurezza</t>
-  </si>
-  <si>
-    <t>Riconoscere e gestire sindromi da sospensione tossicità e interazioni farmacologiche</t>
-  </si>
-  <si>
     <t>Riabilitazione psicosociale e recovery</t>
   </si>
   <si>
-    <t>Strutturare interventi riabilitativi orientati al recupero dell’autonomia personale e sociale</t>
-  </si>
-  <si>
-    <t>Valutare funzionamento globale e obiettivi di recovery attraverso strumenti validati</t>
-  </si>
-  <si>
-    <t>Gestire percorsi terapeutico-riabilitativi in contesti territoriali e residenziali</t>
-  </si>
-  <si>
     <t>Tutela legale e misure restrittive</t>
   </si>
   <si>
-    <t>Applicare normativa su trattamento sanitario obbligatorio garantendo tutela dei diritti dell’assistito</t>
-  </si>
-  <si>
-    <t>Gestire procedure di contenzione nel rispetto di criteri clinici legali e di sicurezza</t>
-  </si>
-  <si>
-    <t>Documentare eventi critici e interventi restrittivi secondo standard normativi</t>
-  </si>
-  <si>
     <t>PSI1</t>
   </si>
   <si>
@@ -1347,6 +1278,153 @@
   </si>
   <si>
     <t>Coordinare il percorso del donatore per garantire continuità di monitoraggio e rispetto dei tempi di ischemia</t>
+  </si>
+  <si>
+    <t>Condurre valutazione dello stato mentale in acuzie utilizzando framework e strumenti di emergenza raccogliendo dati e formulando valutazione infermieristica e interventi condivisi con équipe e rete</t>
+  </si>
+  <si>
+    <t>Costruire un setting terapeutico dinamico adattato a condizioni emotive e psicopatologiche garantendo riservatezza e applicazione della normativa privacy</t>
+  </si>
+  <si>
+    <t>Definire grado di urgenza e priorità assistenziale evitando decisioni affrettate e rivalutando dinamicamente rischio e bisogni clinici</t>
+  </si>
+  <si>
+    <t>Identificare con l’équipe segni prodromici di crisi e rischi prevedibili impostando un problem setting orientato alla riduzione del rischio e al recupero di controllo</t>
+  </si>
+  <si>
+    <t>Attuare tecniche di de-escalation mantenendo prossemica e postura adeguate evitando simmetria richiedendo supporto quando necessario e modulando presenza di persone significative</t>
+  </si>
+  <si>
+    <t>Accogliere e contenere emotivamente assistito e familiari attuando interventi terapeutici tempestivi per limitare rischi per la persona l’ambiente e la rete e prestando primo soccorso in caso di lesioni significative</t>
+  </si>
+  <si>
+    <t>Monitorare efficacia e tollerabilità dei trattamenti psicofarmacologici valutando risposta clinica e effetti indesiderati</t>
+  </si>
+  <si>
+    <t>Gestire terapie long acting e contenimento farmacologico secondo protocolli monitorando parametri clinici sicurezza ed esiti</t>
+  </si>
+  <si>
+    <t>Condurre o co-condurre attività di gruppo psicoeducative social skills training o centrate su compito adattando setting e obiettivi riabilitativi</t>
+  </si>
+  <si>
+    <t>Integrare progetti terapeutici e socio-riabilitativi attivando azioni partecipative orientate al fare comunità e alla continuità dei percorsi</t>
+  </si>
+  <si>
+    <t>Attuare interventi di consolidamento nei punti fragili della rete prevenendo frammentazione e garantendo continuità in contesti territoriali e residenziali</t>
+  </si>
+  <si>
+    <t>Coordinare i percorsi di accesso ai servizi in urgenza nel rispetto di diritti umani e civili applicando riferimenti etico-giuridici inclusa normativa su tso quando indicato</t>
+  </si>
+  <si>
+    <t>Gestire contenzione ambientale meccanica relazionale e farmacologica applicando criteri clinici legali e di sicurezza con monitoraggio e rivalutazione della criticità</t>
+  </si>
+  <si>
+    <t>Documentare eventi critici e interventi restrittivi garantendo tracciabilità motivazione clinica tempi rivalutazioni e esiti secondo standard normativi</t>
+  </si>
+  <si>
+    <t>Riconoscere e gestire i pazienti con sintomi di astinenza da alcol o sostanze attraverso un approccio strutturato</t>
+  </si>
+  <si>
+    <t>PSF4</t>
+  </si>
+  <si>
+    <t>Riconoscere e gestire sindromi da sospensione o tossicità o accumulo di farmaci e interazioni farmacologiche</t>
+  </si>
+  <si>
+    <t>Lavoro di rete</t>
+  </si>
+  <si>
+    <t>Individua,ricerca eapplica forme di azione collettiva e forme di azioni partecipativa volte al fare "Comunità",convolgendo tutti gli attori presenti nel territorio di riferimento</t>
+  </si>
+  <si>
+    <t>Integra i progetti per la  salute mentale unificando percorsi clinici riabilitativi nei contesti di vita e istituzionali ,superando la dicotomia tra cura e reinserimento sociale</t>
+  </si>
+  <si>
+    <t>Utilizzare un approccio strutturato per valutare e dare priorità iniziale ai pazienti con problemi di salute mentale acuta (triage),utilizzando strumenti di valutazione concordati localmente</t>
+  </si>
+  <si>
+    <t>Realizza un clima di accettazione ,apertura e accoglienza,instaurando una relazione terapeutica</t>
+  </si>
+  <si>
+    <t>Adatta le tecniche comunicative verbali e non verbali in relazione all'intelocutore</t>
+  </si>
+  <si>
+    <t>Partecipa e condivide, con la giusta distanza emotiva, le sensazioni del paziente ,per aiutarlo a vedere più chiaramente le proprie preoccupazioni e difficoltà</t>
+  </si>
+  <si>
+    <t>RET1</t>
+  </si>
+  <si>
+    <t>REL1</t>
+  </si>
+  <si>
+    <t>RET2</t>
+  </si>
+  <si>
+    <t>RET3</t>
+  </si>
+  <si>
+    <t>Relazione</t>
+  </si>
+  <si>
+    <t>REL2</t>
+  </si>
+  <si>
+    <t>REL3</t>
+  </si>
+  <si>
+    <t>ALL4</t>
+  </si>
+  <si>
+    <t>Gestire  la pratica dello skin to skin, del roaming in e della Kangaroo terapy</t>
+  </si>
+  <si>
+    <t>NEON4</t>
+  </si>
+  <si>
+    <t>Riconoscere e gestire episodi di instabilità metabolica o termica</t>
+  </si>
+  <si>
+    <t>Individuare le situazioni di fragilità e di rischio psicosociale, abuso e maltrattamento e se necessario, intervenire e coinvolgere le autorità preposte</t>
+  </si>
+  <si>
+    <t>Valutare il fabbisogno educativo-informativo della donna e pianificare in terventi orientati al sostegno, all’autocura ed al recupero funzionale. Promozione dell’autonomia e delle capacità di autocura della donna e della coppia, nel rispetto dei valori etici, religiosi, culturali e delle risorse di sponibili</t>
+  </si>
+  <si>
+    <t>Capacità di riconoscere e gestire situazioni di emergenza ginecologica e ostetrica, protocolli di sicurezza clinica.</t>
+  </si>
+  <si>
+    <t>Gestione del rischio ostetrico ginecologico</t>
+  </si>
+  <si>
+    <t>Conoscere ed utilizza i protocolli specifici ed i termini di legge relativi all'interruzione di gravidanza volontaria ed alla gestione della paziente con aborto spontano</t>
+  </si>
+  <si>
+    <t>Riconoscere e avviare le procedure riguardanti l'impatto emotivo e fisico di violenza sessuale o stupro</t>
+  </si>
+  <si>
+    <t>RSK1</t>
+  </si>
+  <si>
+    <t>RSK2</t>
+  </si>
+  <si>
+    <t>RSK3</t>
+  </si>
+  <si>
+    <t>RSK5</t>
+  </si>
+  <si>
+    <t>RSK7</t>
+  </si>
+  <si>
+    <t>RSK8</t>
+  </si>
+  <si>
+    <t>Condividere il percorso nascita nei programmi di continuità assistenziale previsti per gravidanza, puerperio ed allattamento e nella prevenzione della depressione post partum</t>
+  </si>
+  <si>
+    <t>Area Ostetrico-Ginecologica</t>
   </si>
 </sst>
 </file>
@@ -1624,11 +1702,17 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="33">
@@ -1668,6 +1752,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFFCCFF"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1996,11 +2085,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F23A4849-ABFA-416A-B95E-9573BC325A40}">
-  <dimension ref="A1:D190"/>
+  <dimension ref="A1:D202"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.6640625" customWidth="1"/>
-    <col min="2" max="2" width="52.44140625" customWidth="1"/>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="2" width="40.44140625" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="109.44140625" customWidth="1"/>
   </cols>
@@ -2609,7 +2698,7 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>391</v>
+        <v>368</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>119</v>
@@ -2623,7 +2712,7 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>391</v>
+        <v>368</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>119</v>
@@ -2637,7 +2726,7 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>391</v>
+        <v>368</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>119</v>
@@ -2651,7 +2740,7 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>391</v>
+        <v>368</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>119</v>
@@ -2665,7 +2754,7 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>391</v>
+        <v>368</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>124</v>
@@ -2679,7 +2768,7 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>391</v>
+        <v>368</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>124</v>
@@ -2693,7 +2782,7 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>391</v>
+        <v>368</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>124</v>
@@ -2707,7 +2796,7 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>391</v>
+        <v>368</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>124</v>
@@ -2721,7 +2810,7 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>391</v>
+        <v>368</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>129</v>
@@ -2735,7 +2824,7 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>391</v>
+        <v>368</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>129</v>
@@ -2749,7 +2838,7 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>391</v>
+        <v>368</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>129</v>
@@ -2763,7 +2852,7 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>391</v>
+        <v>368</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>129</v>
@@ -2777,7 +2866,7 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>392</v>
+        <v>369</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>141</v>
@@ -2791,7 +2880,7 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>392</v>
+        <v>369</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>141</v>
@@ -2805,7 +2894,7 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>392</v>
+        <v>369</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>141</v>
@@ -2819,7 +2908,7 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>392</v>
+        <v>369</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>141</v>
@@ -2833,7 +2922,7 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>392</v>
+        <v>369</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>141</v>
@@ -2847,7 +2936,7 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>392</v>
+        <v>369</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>141</v>
@@ -2861,7 +2950,7 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>392</v>
+        <v>369</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>141</v>
@@ -2875,7 +2964,7 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>392</v>
+        <v>369</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>149</v>
@@ -2889,7 +2978,7 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>392</v>
+        <v>369</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>149</v>
@@ -2903,7 +2992,7 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>392</v>
+        <v>369</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>149</v>
@@ -2917,7 +3006,7 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>392</v>
+        <v>369</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>149</v>
@@ -2931,7 +3020,7 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>392</v>
+        <v>369</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>154</v>
@@ -2945,7 +3034,7 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>392</v>
+        <v>369</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>154</v>
@@ -2959,7 +3048,7 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>392</v>
+        <v>369</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>154</v>
@@ -2973,7 +3062,7 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>392</v>
+        <v>369</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>154</v>
@@ -2987,7 +3076,7 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>392</v>
+        <v>369</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>159</v>
@@ -3001,7 +3090,7 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
-        <v>392</v>
+        <v>369</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>159</v>
@@ -3015,7 +3104,7 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
-        <v>392</v>
+        <v>369</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>159</v>
@@ -3029,7 +3118,7 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>393</v>
+        <v>370</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>180</v>
@@ -3043,7 +3132,7 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>393</v>
+        <v>370</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>180</v>
@@ -3057,7 +3146,7 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>393</v>
+        <v>370</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>180</v>
@@ -3071,13 +3160,13 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
-        <v>393</v>
+        <v>370</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>180</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>184</v>
@@ -3085,13 +3174,13 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
-        <v>393</v>
+        <v>370</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>180</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>185</v>
@@ -3099,13 +3188,13 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>393</v>
+        <v>370</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>180</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>186</v>
@@ -3113,13 +3202,13 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>393</v>
+        <v>370</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>187</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>202</v>
+        <v>54</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>188</v>
@@ -3127,13 +3216,13 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
-        <v>393</v>
+        <v>370</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>187</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>203</v>
+        <v>55</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>189</v>
@@ -3141,13 +3230,13 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>393</v>
+        <v>370</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>187</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>190</v>
@@ -3155,13 +3244,13 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
-        <v>393</v>
+        <v>370</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>191</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>54</v>
+        <v>199</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>192</v>
@@ -3169,13 +3258,13 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
-        <v>393</v>
+        <v>370</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>191</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>55</v>
+        <v>200</v>
       </c>
       <c r="D84" s="1" t="s">
         <v>193</v>
@@ -3183,1490 +3272,1658 @@
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
-        <v>393</v>
+        <v>370</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>191</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A86" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>195</v>
+      <c r="A86" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>202</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>196</v>
+        <v>218</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A87" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>195</v>
+      <c r="A87" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>202</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>197</v>
+        <v>219</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A88" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>195</v>
+      <c r="A88" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>202</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>198</v>
+        <v>220</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
-        <v>394</v>
+        <v>371</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
-        <v>394</v>
+        <v>371</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
-        <v>394</v>
+        <v>371</v>
       </c>
       <c r="B91" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="D91" s="2" t="s">
         <v>209</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
-        <v>394</v>
+        <v>371</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
-        <v>394</v>
+        <v>371</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
-        <v>394</v>
+        <v>371</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
-        <v>394</v>
+        <v>371</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
-        <v>394</v>
+        <v>371</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>214</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
-        <v>394</v>
+        <v>371</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>214</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
-        <v>394</v>
+        <v>371</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>214</v>
       </c>
       <c r="C98" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A99" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B99" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="D98" s="2" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A99" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="B99" s="2" t="s">
-        <v>221</v>
-      </c>
       <c r="C99" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D99" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="D99" s="2" t="s">
-        <v>222</v>
-      </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A100" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="B100" s="2" t="s">
-        <v>221</v>
+      <c r="A100" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>234</v>
       </c>
       <c r="C100" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D100" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="D100" s="2" t="s">
-        <v>223</v>
-      </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A101" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="B101" s="2" t="s">
-        <v>221</v>
+      <c r="A101" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>234</v>
       </c>
       <c r="C101" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D101" s="1" t="s">
         <v>237</v>
-      </c>
-      <c r="D101" s="2" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
-        <v>425</v>
+        <v>402</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
-        <v>425</v>
+        <v>402</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
-        <v>425</v>
+        <v>402</v>
       </c>
       <c r="B104" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D104" s="1" t="s">
         <v>241</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D104" s="1" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
-        <v>425</v>
+        <v>402</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="C105" s="2" t="s">
-        <v>51</v>
+        <v>240</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
-        <v>425</v>
+        <v>402</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="C106" s="2" t="s">
-        <v>52</v>
+        <v>240</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
-        <v>425</v>
+        <v>402</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
-        <v>425</v>
+        <v>402</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
-        <v>425</v>
+        <v>402</v>
       </c>
       <c r="B109" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="D109" s="1" t="s">
         <v>247</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
-        <v>425</v>
+        <v>402</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>48</v>
+        <v>251</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
-        <v>425</v>
+        <v>402</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>49</v>
+        <v>252</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
-        <v>425</v>
+        <v>402</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>253</v>
+        <v>406</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>257</v>
+        <v>408</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>254</v>
+        <v>411</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
-        <v>425</v>
+        <v>402</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>253</v>
+        <v>406</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>258</v>
+        <v>409</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>255</v>
+        <v>407</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
-        <v>425</v>
+        <v>402</v>
       </c>
       <c r="B114" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A115" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="B115" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C114" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="D114" s="1" t="s">
+      <c r="C115" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A116" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A117" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="D117" s="2" t="s">
         <v>256</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A115" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="B115" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="C115" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="D115" s="1" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A116" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="B116" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="C116" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="D116" s="1" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A117" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="B117" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="C117" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
-        <v>426</v>
+        <v>403</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>277</v>
+        <v>446</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>261</v>
+        <v>445</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
-        <v>426</v>
+        <v>403</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
-        <v>426</v>
+        <v>403</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
-        <v>426</v>
+        <v>403</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
-        <v>426</v>
+        <v>403</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>281</v>
+        <v>444</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>266</v>
+        <v>286</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
-        <v>426</v>
+        <v>403</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
-        <v>426</v>
+        <v>403</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
-        <v>426</v>
+        <v>403</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>270</v>
+        <v>447</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
-        <v>426</v>
+        <v>403</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
-        <v>426</v>
+        <v>403</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
-        <v>426</v>
+        <v>403</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
-        <v>426</v>
+        <v>403</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>299</v>
+        <v>279</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>291</v>
+        <v>266</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
-        <v>426</v>
+        <v>403</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
-        <v>426</v>
+        <v>403</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
-        <v>426</v>
+        <v>403</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>273</v>
+        <v>292</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>289</v>
+        <v>302</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>276</v>
+        <v>293</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
-        <v>426</v>
+        <v>403</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
-        <v>426</v>
+        <v>403</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
-        <v>426</v>
+        <v>403</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
-        <v>426</v>
+        <v>403</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
-        <v>426</v>
+        <v>403</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
-        <v>426</v>
+        <v>403</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
-        <v>426</v>
+        <v>403</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
-        <v>426</v>
+        <v>403</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>309</v>
+        <v>284</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
-        <v>426</v>
+        <v>403</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
-        <v>426</v>
+        <v>403</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
-        <v>426</v>
+        <v>403</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="s">
-        <v>426</v>
+        <v>403</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="s">
-        <v>426</v>
+        <v>403</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A146" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="B146" s="2" t="s">
-        <v>303</v>
+      <c r="A146" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>336</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="D146" s="2" t="s">
-        <v>297</v>
+        <v>354</v>
+      </c>
+      <c r="D146" s="1" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A147" s="2" t="s">
-        <v>427</v>
+      <c r="A147" s="1" t="s">
+        <v>405</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="C147" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A148" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A149" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A150" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A151" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A152" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="D152" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="D147" s="1" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A148" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="B148" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="C148" s="2" t="s">
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A153" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="B153" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="D148" s="1" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A149" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="B149" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="C149" s="2" t="s">
+      <c r="C153" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="D153" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="D149" s="1" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A150" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="B150" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="C150" s="2" t="s">
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A154" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="C154" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="D154" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="D150" s="1" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A151" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="B151" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="C151" s="2" t="s">
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A155" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="D155" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="D151" s="1" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A152" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="B152" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="C152" s="2" t="s">
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A156" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="D156" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="D152" s="1" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A153" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="B153" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="C153" s="2" t="s">
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A157" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="B157" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="D153" s="1" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A154" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="B154" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="C154" s="2" t="s">
+      <c r="C157" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="D157" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="D154" s="1" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A155" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="B155" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="C155" s="2" t="s">
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A158" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="C158" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="D158" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="D155" s="1" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A156" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="B156" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="C156" s="2" t="s">
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A159" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="C159" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="D159" s="1" t="s">
         <v>353</v>
-      </c>
-      <c r="D156" s="1" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A157" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="B157" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="C157" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="D157" s="1" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A158" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="B158" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="C158" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="D158" s="1" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A159" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="B159" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="C159" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="D159" s="1" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A160" s="2" t="s">
-        <v>427</v>
+        <v>372</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="C160" s="2" t="s">
-        <v>357</v>
+        <v>373</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>393</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>342</v>
+        <v>374</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A161" s="2" t="s">
-        <v>427</v>
+        <v>372</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="C161" s="2" t="s">
-        <v>358</v>
+        <v>373</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>394</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>343</v>
+        <v>375</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A162" s="1" t="s">
-        <v>428</v>
+      <c r="A162" s="2" t="s">
+        <v>372</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="C162" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="D162" s="1" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A163" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="B163" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="D162" s="1" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A163" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="B163" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="C163" s="2" t="s">
+      <c r="C163" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D163" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="D163" s="1" t="s">
-        <v>361</v>
-      </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A164" s="1" t="s">
-        <v>428</v>
+      <c r="A164" s="2" t="s">
+        <v>372</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="C164" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D164" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="D164" s="1" t="s">
-        <v>362</v>
-      </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A165" s="1" t="s">
-        <v>428</v>
+      <c r="A165" s="2" t="s">
+        <v>372</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="C165" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D165" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="D165" s="1" t="s">
-        <v>363</v>
-      </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A166" s="1" t="s">
-        <v>428</v>
+      <c r="A166" s="2" t="s">
+        <v>372</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="C166" s="2" t="s">
         <v>381</v>
       </c>
+      <c r="C166" s="1" t="s">
+        <v>396</v>
+      </c>
       <c r="D166" s="1" t="s">
-        <v>365</v>
+        <v>382</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A167" s="1" t="s">
-        <v>428</v>
+      <c r="A167" s="2" t="s">
+        <v>372</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="C167" s="2" t="s">
-        <v>382</v>
+        <v>381</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>397</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>366</v>
+        <v>383</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A168" s="1" t="s">
-        <v>428</v>
+      <c r="A168" s="2" t="s">
+        <v>372</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="C168" s="2" t="s">
-        <v>383</v>
+        <v>381</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>398</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>367</v>
+        <v>384</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A169" s="1" t="s">
-        <v>428</v>
+      <c r="A169" s="2" t="s">
+        <v>372</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="C169" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>399</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>369</v>
+        <v>392</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A170" s="1" t="s">
-        <v>428</v>
+      <c r="A170" s="2" t="s">
+        <v>372</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="C170" s="2" t="s">
         <v>385</v>
       </c>
+      <c r="C170" s="1" t="s">
+        <v>400</v>
+      </c>
       <c r="D170" s="1" t="s">
-        <v>370</v>
+        <v>386</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A171" s="1" t="s">
-        <v>428</v>
+      <c r="A171" s="2" t="s">
+        <v>372</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="C171" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>401</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>371</v>
+        <v>387</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A172" s="1" t="s">
-        <v>428</v>
+      <c r="A172" s="2" t="s">
+        <v>372</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="C172" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
+      </c>
+      <c r="C172" s="1" t="s">
+        <v>231</v>
       </c>
       <c r="D172" s="1" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A173" s="2" t="s">
         <v>372</v>
       </c>
-    </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A173" s="1" t="s">
-        <v>428</v>
-      </c>
       <c r="B173" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="C173" s="2" t="s">
         <v>388</v>
       </c>
+      <c r="C173" s="1" t="s">
+        <v>232</v>
+      </c>
       <c r="D173" s="1" t="s">
-        <v>374</v>
+        <v>390</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A174" s="1" t="s">
-        <v>428</v>
+      <c r="A174" s="2" t="s">
+        <v>372</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="C174" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
+      </c>
+      <c r="C174" s="1" t="s">
+        <v>233</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>375</v>
+        <v>391</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A175" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="B175" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="C175" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D175" s="1" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A176" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="B176" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="C176" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="D176" s="1" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A177" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="D177" s="1" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A178" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="D178" s="1" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A179" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="B179" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="C179" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="D179" s="1" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A180" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="B180" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="C180" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="D180" s="1" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A181" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="B181" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="C181" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="D181" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A182" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="B182" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="C182" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="D182" s="1" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A183" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="B183" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="C183" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="D183" s="1" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A184" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="B184" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="C184" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="B175" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="C175" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="D175" s="1" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A176" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="B176" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="C176" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="D176" s="1" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A177" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="B177" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="C177" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="D177" s="1" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A178" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="B178" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="C178" s="1" t="s">
-        <v>418</v>
-      </c>
-      <c r="D178" s="1" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A179" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="B179" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="C179" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="D179" s="1" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A180" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="B180" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="C180" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="D180" s="1" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A181" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="B181" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="C181" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="D181" s="1" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A182" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="B182" s="1" t="s">
+      <c r="D184" s="1" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A185" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="C182" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="D182" s="1" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A183" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="B183" s="1" t="s">
+      <c r="B185" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="C185" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="D185" s="1" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A186" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="C183" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="D183" s="1" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A184" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="B184" s="1" t="s">
+      <c r="B186" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="C186" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="D186" s="1" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A187" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="C184" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="D184" s="1" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A185" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="B185" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="C185" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="D185" s="1" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A186" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="B186" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="C186" s="1" t="s">
+      <c r="B187" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="C187" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="D187" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="D186" s="1" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A187" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="B187" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="C187" s="1" t="s">
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A188" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="B188" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="C188" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="D188" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="D187" s="1" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A188" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="B188" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="C188" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="D188" s="1" t="s">
-        <v>412</v>
-      </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A189" s="2" t="s">
-        <v>395</v>
+      <c r="A189" s="1" t="s">
+        <v>404</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>411</v>
+        <v>320</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>239</v>
+        <v>334</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A190" s="2" t="s">
-        <v>395</v>
+      <c r="A190" s="1" t="s">
+        <v>404</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>411</v>
+        <v>320</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>240</v>
+        <v>335</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>414</v>
+        <v>426</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A191" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="B191" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="C191" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="D191" s="1" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A192" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="B192" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="C192" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="D192" s="4" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A193" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="B193" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="C193" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="D193" s="1" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A194" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="B194" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="C194" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="D194" s="1" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A195" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="B195" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="C195" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="D195" s="1" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A196" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="B196" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="C196" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="D196" s="1" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A197" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="B197" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C197" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="D197" s="2" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A198" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="B198" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C198" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="D198" s="2" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A199" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="B199" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C199" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="D199" s="2" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A200" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="B200" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C200" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="D200" s="2" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A201" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="B201" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C201" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="D201" s="2" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A202" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="B202" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C202" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="D202" s="2" t="s">
+        <v>453</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D190" xr:uid="{F23A4849-ABFA-416A-B95E-9573BC325A40}"/>
+  <autoFilter ref="A1:D196" xr:uid="{F23A4849-ABFA-416A-B95E-9573BC325A40}"/>
   <phoneticPr fontId="20" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
